--- a/Tabelas/casos_por_estado.xlsx
+++ b/Tabelas/casos_por_estado.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D5" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D6" t="n">
         <v>4.38</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D7" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>1238</v>
       </c>
       <c r="D8" t="n">
-        <v>19.86</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D9" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D10" t="n">
-        <v>4.65</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
         <v>1.12</v>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="D12" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="13">
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D15" t="n">
         <v>3.84</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="17">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="18">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="19">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D19" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>588</v>
+        <v>615</v>
       </c>
       <c r="D20" t="n">
-        <v>10.13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>1.46</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="24">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D24" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="25">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D25" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="26">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D26" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="27">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="D27" t="n">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="28">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5805</v>
+        <v>6148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
